--- a/data_voor_swing/aggregatietabellen/woningmarkt_gewest.xlsx
+++ b/data_voor_swing/aggregatietabellen/woningmarkt_gewest.xlsx
@@ -1,57 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <workbookPr showObjects="all" updateLinks="userSet" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" xWindow="480" yWindow="75" windowWidth="18075" windowHeight="12525" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="woningmarkt_gewest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" calcMode="auto" refMode="A1" iterateCount="100"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.000000"/>
-    <numFmt numFmtId="171" formatCode="0.0000000"/>
-    <numFmt numFmtId="172" formatCode="0.00000000"/>
-    <numFmt numFmtId="173" formatCode="0.000000000"/>
-    <numFmt numFmtId="174" formatCode="0.0000000000"/>
-    <numFmt numFmtId="175" formatCode="0.00000000000"/>
-    <numFmt numFmtId="176" formatCode="0.000000000000"/>
-    <numFmt numFmtId="177" formatCode="0.0000000000000"/>
-    <numFmt numFmtId="178" formatCode="0.00000000000000"/>
-    <numFmt numFmtId="179" formatCode="0.000000000000000"/>
-    <numFmt numFmtId="180" formatCode="0.0000000000000000"/>
-  </numFmts>
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,41 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -381,133 +420,159 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" s="0" outlineLevel="0">
-      <c r="A1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>woningmarkt</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gewest</t>
         </is>
       </c>
     </row>
-    <row r="2" spans="1:2" s="0" outlineLevel="0">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>BLM</t>
         </is>
       </c>
-      <c r="B2" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="0" outlineLevel="0">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>RWM_MLO</t>
         </is>
       </c>
-      <c r="B3" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="0" outlineLevel="0">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>RWM_MLW</t>
         </is>
       </c>
-      <c r="B4" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="0" outlineLevel="0">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>RWM_NL</t>
         </is>
       </c>
-      <c r="B5" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="0" outlineLevel="0">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>RWM_NOL</t>
         </is>
       </c>
-      <c r="B6" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="0" outlineLevel="0">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>RWM_NWL</t>
         </is>
       </c>
-      <c r="B7" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="0" outlineLevel="0">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>RWM_OL</t>
         </is>
       </c>
-      <c r="B8" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="0" outlineLevel="0">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>RWM_V</t>
         </is>
       </c>
-      <c r="B9" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="0" outlineLevel="0">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>RWM_WL</t>
         </is>
       </c>
-      <c r="B10" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="0" outlineLevel="0">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>RWM_ZOL</t>
         </is>
       </c>
-      <c r="B11" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="0" outlineLevel="0">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>RWM_ZWL</t>
         </is>
       </c>
-      <c r="B12" s="23">
-        <v>2000</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>